--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 61 D100 Spring 2024 24GE03I53 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 61 D100 Spring 2024 24GE03I53 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GL Lab User\Desktop\GLNPO Zooplankton Counts\Erie\Spring 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FB33DD-9599-48A0-BC5E-4E5CA37B788E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AECFD3-EEDE-4346-8480-6C4CA48C4E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{CDF3370C-E844-4406-9D54-E73F8638BE6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CDF3370C-E844-4406-9D54-E73F8638BE6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AH$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$253</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12126" r:id="rId2"/>
+    <pivotCache cacheId="4" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -511,7 +511,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -528,7 +528,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -5692,7 +5691,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E815C56-76AD-4CCF-8B32-4019688135AA}" name="PivotTable9" cacheId="12126" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E815C56-76AD-4CCF-8B32-4019688135AA}" name="PivotTable9" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:W26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6166,21 +6165,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12ADBFD-46A6-469D-8ACF-BB4AB9C688AC}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH253"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6236,7 +6236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6415,17 +6415,17 @@
       <c r="T4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4">
         <v>4</v>
       </c>
-      <c r="V4" s="10">
-        <v>2</v>
-      </c>
-      <c r="W4" s="10">
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6480,17 +6480,17 @@
       <c r="T5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="U5" s="10">
-        <v>1</v>
-      </c>
-      <c r="V5" s="10">
-        <v>1</v>
-      </c>
-      <c r="W5" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6545,17 +6545,17 @@
       <c r="T6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6">
         <v>3</v>
       </c>
-      <c r="V6" s="10">
-        <v>2</v>
-      </c>
-      <c r="W6" s="10">
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6610,17 +6610,17 @@
       <c r="T7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="U7" s="10">
-        <v>1</v>
-      </c>
-      <c r="V7" s="10">
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
         <v>0</v>
       </c>
-      <c r="W7" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6675,17 +6675,17 @@
       <c r="T8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="U8" s="10">
-        <v>18</v>
-      </c>
-      <c r="V8" s="10">
+      <c r="U8">
+        <v>18</v>
+      </c>
+      <c r="V8">
         <v>11</v>
       </c>
-      <c r="W8" s="10">
+      <c r="W8">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6740,17 +6740,17 @@
       <c r="T9" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="U9" s="10">
-        <v>1</v>
-      </c>
-      <c r="V9" s="10">
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
         <v>0</v>
       </c>
-      <c r="W9" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6805,17 +6805,17 @@
       <c r="T10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="U10" s="10">
+      <c r="U10">
         <v>14</v>
       </c>
-      <c r="V10" s="10">
-        <v>22</v>
-      </c>
-      <c r="W10" s="10">
+      <c r="V10">
+        <v>22</v>
+      </c>
+      <c r="W10">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6870,17 +6870,17 @@
       <c r="T11" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="U11" s="10">
+      <c r="U11">
         <v>3</v>
       </c>
-      <c r="V11" s="10">
+      <c r="V11">
         <v>4</v>
       </c>
-      <c r="W11" s="10">
+      <c r="W11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6938,17 +6938,17 @@
       <c r="T12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U12" s="10">
+      <c r="U12">
         <v>7</v>
       </c>
-      <c r="V12" s="10">
+      <c r="V12">
         <v>3</v>
       </c>
-      <c r="W12" s="10">
+      <c r="W12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -7003,17 +7003,17 @@
       <c r="T13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="U13" s="10">
+      <c r="U13">
         <v>4</v>
       </c>
-      <c r="V13" s="10">
-        <v>1</v>
-      </c>
-      <c r="W13" s="10">
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7068,17 +7068,17 @@
       <c r="T14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="10">
+      <c r="U14">
         <v>7</v>
       </c>
-      <c r="V14" s="10">
+      <c r="V14">
         <v>14</v>
       </c>
-      <c r="W14" s="10">
+      <c r="W14">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7133,17 +7133,17 @@
       <c r="T15" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="U15" s="10">
+      <c r="U15">
         <v>34</v>
       </c>
-      <c r="V15" s="10">
+      <c r="V15">
         <v>37</v>
       </c>
-      <c r="W15" s="10">
+      <c r="W15">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -7198,17 +7198,17 @@
       <c r="T16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="10">
+      <c r="U16">
         <v>49</v>
       </c>
-      <c r="V16" s="10">
+      <c r="V16">
         <v>53</v>
       </c>
-      <c r="W16" s="10">
+      <c r="W16">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7263,17 +7263,17 @@
       <c r="T17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="U17" s="10">
+      <c r="U17">
         <v>27</v>
       </c>
-      <c r="V17" s="10">
+      <c r="V17">
         <v>32</v>
       </c>
-      <c r="W17" s="10">
+      <c r="W17">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7328,17 +7328,17 @@
       <c r="T18" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="U18" s="10">
-        <v>2</v>
-      </c>
-      <c r="V18" s="10">
-        <v>2</v>
-      </c>
-      <c r="W18" s="10">
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>2</v>
+      </c>
+      <c r="W18">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7393,17 +7393,17 @@
       <c r="T19" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="U19" s="10">
+      <c r="U19">
         <v>3</v>
       </c>
-      <c r="V19" s="10">
-        <v>1</v>
-      </c>
-      <c r="W19" s="10">
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7461,17 +7461,17 @@
       <c r="T20" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="U20" s="10">
-        <v>1</v>
-      </c>
-      <c r="V20" s="10">
-        <v>1</v>
-      </c>
-      <c r="W20" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7526,17 +7526,17 @@
       <c r="T21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="U21" s="10">
-        <v>1</v>
-      </c>
-      <c r="V21" s="10">
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
         <v>0</v>
       </c>
-      <c r="W21" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7591,17 +7591,17 @@
       <c r="T22" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="U22" s="10">
+      <c r="U22">
         <v>7</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22">
         <v>8</v>
       </c>
-      <c r="W22" s="10">
+      <c r="W22">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7656,17 +7656,17 @@
       <c r="T23" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="U23" s="10">
+      <c r="U23">
         <v>0</v>
       </c>
-      <c r="V23" s="10">
-        <v>1</v>
-      </c>
-      <c r="W23" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7721,17 +7721,17 @@
       <c r="T24" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="U24" s="10">
+      <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" s="10">
-        <v>1</v>
-      </c>
-      <c r="W24" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7786,17 +7786,17 @@
       <c r="T25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="U25" s="10">
+      <c r="U25">
         <v>8</v>
       </c>
-      <c r="V25" s="10">
+      <c r="V25">
         <v>4</v>
       </c>
-      <c r="W25" s="10">
+      <c r="W25">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7851,17 +7851,17 @@
       <c r="T26" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="U26" s="10">
+      <c r="U26">
         <v>195</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26">
         <v>200</v>
       </c>
-      <c r="W26" s="10">
+      <c r="W26">
         <v>395</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7966,13 +7966,13 @@
       <c r="Q28">
         <v>1</v>
       </c>
-      <c r="T28" s="11" t="s">
+      <c r="T28" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+    </row>
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -8024,17 +8024,17 @@
       <c r="Q29">
         <v>1</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="T29" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="U29" s="13" t="s">
+      <c r="U29" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="V29" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V29" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -8086,15 +8086,15 @@
       <c r="Q30">
         <v>1</v>
       </c>
-      <c r="T30" s="11"/>
-      <c r="U30" s="13" t="s">
+      <c r="T30" s="10"/>
+      <c r="U30" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="V30" s="12">
+      <c r="V30" s="11">
         <v>0.998</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -8146,17 +8146,17 @@
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="T31" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="U31" s="13" t="s">
+      <c r="U31" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="V31" s="12">
+      <c r="V31" s="11">
         <v>0.996</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -8208,15 +8208,15 @@
       <c r="Q32">
         <v>1</v>
       </c>
-      <c r="T32" s="12"/>
-      <c r="U32" s="13" t="s">
+      <c r="T32" s="11"/>
+      <c r="U32" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="V32" s="12">
+      <c r="V32" s="11">
         <v>0.996</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -8268,15 +8268,15 @@
       <c r="Q33">
         <v>1</v>
       </c>
-      <c r="T33" s="11" t="s">
+      <c r="T33" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="U33" s="13" t="s">
+      <c r="U33" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="V33" s="14"/>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="V33" s="13"/>
+    </row>
+    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8328,15 +8328,15 @@
       <c r="Q34">
         <v>1</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="T34" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="U34" s="12" t="s">
+      <c r="U34" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="V34" s="12"/>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="V34" s="11"/>
+    </row>
+    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8388,25 +8388,25 @@
       <c r="Q35">
         <v>1</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="T35" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12"/>
-      <c r="Y35" s="12"/>
-      <c r="Z35" s="12"/>
-      <c r="AA35" s="12"/>
-      <c r="AB35" s="12"/>
-      <c r="AC35" s="12"/>
-      <c r="AD35" s="12"/>
-      <c r="AE35" s="12"/>
-      <c r="AF35" s="12"/>
-      <c r="AG35" s="12"/>
-      <c r="AH35" s="12"/>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11"/>
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11"/>
+      <c r="AD35" s="11"/>
+      <c r="AE35" s="11"/>
+      <c r="AF35" s="11"/>
+      <c r="AG35" s="11"/>
+      <c r="AH35" s="11"/>
+    </row>
+    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8939,7 +8939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9896,7 +9896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -10055,7 +10055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10850,7 +10850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -11118,7 +11118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11333,7 +11333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>24</v>
       </c>
       <c r="K95" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -11598,7 +11598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12340,7 +12340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12446,7 +12446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12711,7 +12711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12817,7 +12817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13453,7 +13453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13506,7 +13506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13559,7 +13559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -14254,7 +14254,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14360,7 +14360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14681,7 +14681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14734,7 +14734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14946,7 +14946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14999,7 +14999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -15108,7 +15108,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -15161,7 +15161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -15267,7 +15267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -15323,7 +15323,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15376,7 +15376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15429,7 +15429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15482,7 +15482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15588,7 +15588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15641,7 +15641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15694,7 +15694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15909,7 +15909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15962,7 +15962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -16124,7 +16124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -16177,7 +16177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16448,7 +16448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16501,7 +16501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16663,7 +16663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16928,7 +16928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -17087,7 +17087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -17140,7 +17140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17302,7 +17302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17355,7 +17355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17461,7 +17461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17514,7 +17514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17620,7 +17620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17726,7 +17726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17779,7 +17779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17832,7 +17832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17885,7 +17885,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17991,7 +17991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -18044,7 +18044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -18097,7 +18097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -18153,7 +18153,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -18206,7 +18206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -18259,7 +18259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -18315,7 +18315,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18371,7 +18371,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18477,7 +18477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18530,7 +18530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18583,7 +18583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -18851,7 +18851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -18907,7 +18907,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -19013,7 +19013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -19069,7 +19069,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -19175,7 +19175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -19281,7 +19281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -19334,7 +19334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -19493,7 +19493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -19546,7 +19546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -19599,7 +19599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -19652,7 +19652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -19705,7 +19705,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -19758,7 +19758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>18</v>
       </c>
@@ -19811,7 +19811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="5" t="s">
         <v>18</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="5" t="s">
         <v>18</v>
       </c>
@@ -19917,7 +19917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
         <v>18</v>
       </c>
@@ -19970,7 +19970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>18</v>
       </c>
@@ -20024,6 +20024,19 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R253" xr:uid="{D12ADBFD-46A6-469D-8ACF-BB4AB9C688AC}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="LEOMINU"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="12">
+      <filters>
+        <filter val="CAL"/>
+        <filter val="CYC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>